--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132321168</v>
       </c>
       <c r="B2" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>132321210</v>
       </c>
       <c r="B3" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>132321171</v>
       </c>
       <c r="B4" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>132321212</v>
       </c>
       <c r="B6" t="n">
-        <v>58320</v>
+        <v>58322</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>132321145</v>
       </c>
       <c r="B7" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,32 +1416,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132321211</v>
+        <v>132321144</v>
       </c>
       <c r="B8" t="n">
-        <v>58320</v>
+        <v>58109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1450,14 +1450,10 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1471,10 +1467,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335168</v>
+        <v>335186</v>
       </c>
       <c r="R8" t="n">
-        <v>6542019</v>
+        <v>6541956</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1511,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare granskog.</t>
+          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,7 +1521,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321144</v>
+        <v>132321211</v>
       </c>
       <c r="B9" t="n">
-        <v>58107</v>
+        <v>58322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1577,10 +1578,14 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1594,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335186</v>
+        <v>335168</v>
       </c>
       <c r="R9" t="n">
-        <v>6541956</v>
+        <v>6542019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,7 +1639,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>1 hane med sång i något tätare granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,12 +1653,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1671,61 +1671,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321143</v>
+        <v>132321126</v>
       </c>
       <c r="B10" t="n">
-        <v>58107</v>
+        <v>96328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335257</v>
+        <v>335020</v>
       </c>
       <c r="R10" t="n">
-        <v>6541801</v>
+        <v>6541936</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,7 +1750,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>Sparsamt i äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,17 +1759,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1799,49 +1783,61 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321126</v>
+        <v>132321143</v>
       </c>
       <c r="B11" t="n">
-        <v>96325</v>
+        <v>58109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335020</v>
+        <v>335257</v>
       </c>
       <c r="R11" t="n">
-        <v>6541936</v>
+        <v>6541801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,7 +1874,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sparsamt i äldre granskog.</t>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,13 +1883,17 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -1671,49 +1671,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321126</v>
+        <v>132321143</v>
       </c>
       <c r="B10" t="n">
-        <v>96328</v>
+        <v>58109</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335020</v>
+        <v>335257</v>
       </c>
       <c r="R10" t="n">
-        <v>6541936</v>
+        <v>6541801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,7 +1762,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt i äldre granskog.</t>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,13 +1771,17 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,61 +1799,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321143</v>
+        <v>132321126</v>
       </c>
       <c r="B11" t="n">
-        <v>58109</v>
+        <v>96328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335257</v>
+        <v>335020</v>
       </c>
       <c r="R11" t="n">
-        <v>6541801</v>
+        <v>6541936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,7 +1878,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>Sparsamt i äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,17 +1887,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321168</v>
+        <v>132321210</v>
       </c>
       <c r="B2" t="n">
-        <v>97963</v>
+        <v>58322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335050</v>
+        <v>335133</v>
       </c>
       <c r="R2" t="n">
-        <v>6542012</v>
+        <v>6542070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +770,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I gammal granskog.</t>
+          <t>1 hane med sång i något tätare barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,13 +779,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321210</v>
+        <v>132321168</v>
       </c>
       <c r="B3" t="n">
-        <v>58322</v>
+        <v>97963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,54 +813,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335133</v>
+        <v>335050</v>
       </c>
       <c r="R3" t="n">
-        <v>6542070</v>
+        <v>6542012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare barrblandskog.</t>
+          <t>I gammal granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +890,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1671,61 +1671,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321143</v>
+        <v>132321126</v>
       </c>
       <c r="B10" t="n">
-        <v>58109</v>
+        <v>96328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335257</v>
+        <v>335020</v>
       </c>
       <c r="R10" t="n">
-        <v>6541801</v>
+        <v>6541936</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,7 +1750,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>Sparsamt i äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,17 +1759,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1799,49 +1783,61 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321126</v>
+        <v>132321143</v>
       </c>
       <c r="B11" t="n">
-        <v>96328</v>
+        <v>58109</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335020</v>
+        <v>335257</v>
       </c>
       <c r="R11" t="n">
-        <v>6541936</v>
+        <v>6541801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,7 +1874,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sparsamt i äldre granskog.</t>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,13 +1883,17 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -1416,32 +1416,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132321144</v>
+        <v>132321211</v>
       </c>
       <c r="B8" t="n">
-        <v>58109</v>
+        <v>58322</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1450,10 +1450,14 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1467,10 +1471,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335186</v>
+        <v>335168</v>
       </c>
       <c r="R8" t="n">
-        <v>6541956</v>
+        <v>6542019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>1 hane med sång i något tätare granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,12 +1525,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1544,32 +1543,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321211</v>
+        <v>132321144</v>
       </c>
       <c r="B9" t="n">
-        <v>58322</v>
+        <v>58109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1578,14 +1577,10 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1599,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335168</v>
+        <v>335186</v>
       </c>
       <c r="R9" t="n">
-        <v>6542019</v>
+        <v>6541956</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1634,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare granskog.</t>
+          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,7 +1648,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -1416,32 +1416,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132321211</v>
+        <v>132321144</v>
       </c>
       <c r="B8" t="n">
-        <v>58322</v>
+        <v>58109</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1450,14 +1450,10 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1471,10 +1467,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335168</v>
+        <v>335186</v>
       </c>
       <c r="R8" t="n">
-        <v>6542019</v>
+        <v>6541956</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1511,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare granskog.</t>
+          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,7 +1521,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321144</v>
+        <v>132321211</v>
       </c>
       <c r="B9" t="n">
-        <v>58109</v>
+        <v>58322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1577,10 +1578,14 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1594,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335186</v>
+        <v>335168</v>
       </c>
       <c r="R9" t="n">
-        <v>6541956</v>
+        <v>6542019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,7 +1639,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>1 hane med sång i något tätare granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,12 +1653,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321210</v>
+        <v>132321168</v>
       </c>
       <c r="B2" t="n">
-        <v>58322</v>
+        <v>97971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,54 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335133</v>
+        <v>335050</v>
       </c>
       <c r="R2" t="n">
-        <v>6542070</v>
+        <v>6542012</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare barrblandskog.</t>
+          <t>I gammal granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +763,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321168</v>
+        <v>132321210</v>
       </c>
       <c r="B3" t="n">
-        <v>97963</v>
+        <v>58323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,38 +798,54 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335050</v>
+        <v>335133</v>
       </c>
       <c r="R3" t="n">
-        <v>6542012</v>
+        <v>6542070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I gammal granskog.</t>
+          <t>1 hane med sång i något tätare barrblandskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,13 +891,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,7 +917,7 @@
         <v>132321171</v>
       </c>
       <c r="B4" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,27 +1026,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321158</v>
+        <v>132321212</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>58323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,25 +1054,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335353</v>
+        <v>335044</v>
       </c>
       <c r="R5" t="n">
-        <v>6541857</v>
+        <v>6541992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>1 hane med sång i äldre granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,32 +1135,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1166,27 +1153,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321212</v>
+        <v>132321158</v>
       </c>
       <c r="B6" t="n">
-        <v>58322</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1194,37 +1181,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335044</v>
+        <v>335353</v>
       </c>
       <c r="R6" t="n">
-        <v>6541992</v>
+        <v>6541857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 hane med sång i äldre granskog.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1250,32 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
         <v>132321145</v>
       </c>
       <c r="B7" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>132321211</v>
       </c>
       <c r="B8" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>132321144</v>
       </c>
       <c r="B9" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>132321126</v>
       </c>
       <c r="B10" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>132321143</v>
       </c>
       <c r="B11" t="n">
-        <v>58109</v>
+        <v>58110</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321168</v>
+        <v>132321210</v>
       </c>
       <c r="B2" t="n">
-        <v>97971</v>
+        <v>58323</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335050</v>
+        <v>335133</v>
       </c>
       <c r="R2" t="n">
-        <v>6542012</v>
+        <v>6542070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +770,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I gammal granskog.</t>
+          <t>1 hane med sång i något tätare barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,13 +779,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321210</v>
+        <v>132321168</v>
       </c>
       <c r="B3" t="n">
-        <v>58323</v>
+        <v>97971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,54 +813,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335133</v>
+        <v>335050</v>
       </c>
       <c r="R3" t="n">
-        <v>6542070</v>
+        <v>6542012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare barrblandskog.</t>
+          <t>I gammal granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +890,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321210</v>
+        <v>132321168</v>
       </c>
       <c r="B2" t="n">
-        <v>58323</v>
+        <v>97981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,54 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335133</v>
+        <v>335050</v>
       </c>
       <c r="R2" t="n">
-        <v>6542070</v>
+        <v>6542012</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare barrblandskog.</t>
+          <t>I gammal granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +763,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321168</v>
+        <v>132321210</v>
       </c>
       <c r="B3" t="n">
-        <v>97971</v>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,38 +798,54 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335050</v>
+        <v>335133</v>
       </c>
       <c r="R3" t="n">
-        <v>6542012</v>
+        <v>6542070</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I gammal granskog.</t>
+          <t>1 hane med sång i något tätare barrblandskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,13 +891,12 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,7 +917,7 @@
         <v>132321171</v>
       </c>
       <c r="B4" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>132321212</v>
       </c>
       <c r="B5" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>132321158</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>132321145</v>
       </c>
       <c r="B7" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         <v>132321211</v>
       </c>
       <c r="B8" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1546,7 +1546,7 @@
         <v>132321144</v>
       </c>
       <c r="B9" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1671,49 +1671,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321126</v>
+        <v>132321143</v>
       </c>
       <c r="B10" t="n">
-        <v>96336</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335020</v>
+        <v>335257</v>
       </c>
       <c r="R10" t="n">
-        <v>6541936</v>
+        <v>6541801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,7 +1762,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt i äldre granskog.</t>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,13 +1771,17 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,61 +1799,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321143</v>
+        <v>132321126</v>
       </c>
       <c r="B11" t="n">
-        <v>58110</v>
+        <v>96346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335257</v>
+        <v>335020</v>
       </c>
       <c r="R11" t="n">
-        <v>6541801</v>
+        <v>6541936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,7 +1878,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>Sparsamt i äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,17 +1887,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321168</v>
+        <v>132321210</v>
       </c>
       <c r="B2" t="n">
-        <v>97981</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,38 +686,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335050</v>
+        <v>335133</v>
       </c>
       <c r="R2" t="n">
-        <v>6542012</v>
+        <v>6542070</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +770,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>I gammal granskog.</t>
+          <t>1 hane med sång i något tätare barrblandskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,13 +779,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321210</v>
+        <v>132321168</v>
       </c>
       <c r="B3" t="n">
-        <v>58327</v>
+        <v>97982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,54 +813,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335133</v>
+        <v>335050</v>
       </c>
       <c r="R3" t="n">
-        <v>6542070</v>
+        <v>6542012</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare barrblandskog.</t>
+          <t>I gammal granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,12 +890,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -917,7 +917,7 @@
         <v>132321171</v>
       </c>
       <c r="B4" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1671,61 +1671,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321143</v>
+        <v>132321126</v>
       </c>
       <c r="B10" t="n">
-        <v>58114</v>
+        <v>96347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335257</v>
+        <v>335020</v>
       </c>
       <c r="R10" t="n">
-        <v>6541801</v>
+        <v>6541936</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,7 +1750,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>Sparsamt i äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,17 +1759,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1799,49 +1783,61 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321126</v>
+        <v>132321143</v>
       </c>
       <c r="B11" t="n">
-        <v>96346</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335020</v>
+        <v>335257</v>
       </c>
       <c r="R11" t="n">
-        <v>6541936</v>
+        <v>6541801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,7 +1874,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sparsamt i äldre granskog.</t>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,13 +1883,17 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>132321168</v>
       </c>
       <c r="B3" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>132321171</v>
       </c>
       <c r="B4" t="n">
-        <v>97982</v>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1674,7 +1674,7 @@
         <v>132321126</v>
       </c>
       <c r="B10" t="n">
-        <v>96347</v>
+        <v>96348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -1026,27 +1026,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321212</v>
+        <v>132321158</v>
       </c>
       <c r="B5" t="n">
-        <v>58327</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,37 +1054,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335044</v>
+        <v>335353</v>
       </c>
       <c r="R5" t="n">
-        <v>6541992</v>
+        <v>6541857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1109,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 hane med sång i äldre granskog.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1123,32 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,27 +1166,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321158</v>
+        <v>132321212</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1181,25 +1194,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335353</v>
+        <v>335044</v>
       </c>
       <c r="R6" t="n">
-        <v>6541857</v>
+        <v>6541992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1261,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>1 hane med sång i äldre granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,32 +1275,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -1416,32 +1416,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132321211</v>
+        <v>132321144</v>
       </c>
       <c r="B8" t="n">
-        <v>58327</v>
+        <v>58114</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1450,14 +1450,10 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1471,10 +1467,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335168</v>
+        <v>335186</v>
       </c>
       <c r="R8" t="n">
-        <v>6542019</v>
+        <v>6541956</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1511,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare granskog.</t>
+          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,7 +1521,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321144</v>
+        <v>132321211</v>
       </c>
       <c r="B9" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1577,10 +1578,14 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1594,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335186</v>
+        <v>335168</v>
       </c>
       <c r="R9" t="n">
-        <v>6541956</v>
+        <v>6542019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,7 +1639,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>1 hane med sång i något tätare granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,12 +1653,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132321210</v>
       </c>
       <c r="B2" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>132321168</v>
       </c>
       <c r="B3" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>132321171</v>
       </c>
       <c r="B4" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>132321158</v>
       </c>
       <c r="B5" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>132321212</v>
       </c>
       <c r="B6" t="n">
-        <v>58327</v>
+        <v>58328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>132321145</v>
       </c>
       <c r="B7" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,32 +1416,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132321144</v>
+        <v>132321211</v>
       </c>
       <c r="B8" t="n">
-        <v>58114</v>
+        <v>58328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1450,10 +1450,14 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1467,10 +1471,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335186</v>
+        <v>335168</v>
       </c>
       <c r="R8" t="n">
-        <v>6541956</v>
+        <v>6542019</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>1 hane med sång i något tätare granskog.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,12 +1525,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1544,32 +1543,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321211</v>
+        <v>132321144</v>
       </c>
       <c r="B9" t="n">
-        <v>58327</v>
+        <v>58115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1578,14 +1577,10 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1599,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335168</v>
+        <v>335186</v>
       </c>
       <c r="R9" t="n">
-        <v>6542019</v>
+        <v>6541956</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1639,7 +1634,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare granskog.</t>
+          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1653,7 +1648,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1674,7 +1674,7 @@
         <v>132321126</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>132321143</v>
       </c>
       <c r="B11" t="n">
-        <v>58114</v>
+        <v>58115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>132321168</v>
       </c>
       <c r="B3" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>132321171</v>
       </c>
       <c r="B4" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1671,49 +1671,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321126</v>
+        <v>132321143</v>
       </c>
       <c r="B10" t="n">
-        <v>96349</v>
+        <v>58115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335020</v>
+        <v>335257</v>
       </c>
       <c r="R10" t="n">
-        <v>6541936</v>
+        <v>6541801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,7 +1762,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt i äldre granskog.</t>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,13 +1771,17 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,61 +1799,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321143</v>
+        <v>132321126</v>
       </c>
       <c r="B11" t="n">
-        <v>58115</v>
+        <v>96351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335257</v>
+        <v>335020</v>
       </c>
       <c r="R11" t="n">
-        <v>6541801</v>
+        <v>6541936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,7 +1878,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>Sparsamt i äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,17 +1887,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>132321168</v>
       </c>
       <c r="B3" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>132321171</v>
       </c>
       <c r="B4" t="n">
-        <v>97986</v>
+        <v>97987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,27 +1026,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321158</v>
+        <v>132321212</v>
       </c>
       <c r="B5" t="n">
-        <v>57951</v>
+        <v>58328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,25 +1054,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335353</v>
+        <v>335044</v>
       </c>
       <c r="R5" t="n">
-        <v>6541857</v>
+        <v>6541992</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1121,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>1 hane med sång i äldre granskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,32 +1135,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1166,27 +1153,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321212</v>
+        <v>132321158</v>
       </c>
       <c r="B6" t="n">
-        <v>58328</v>
+        <v>57951</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1194,37 +1181,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335044</v>
+        <v>335353</v>
       </c>
       <c r="R6" t="n">
-        <v>6541992</v>
+        <v>6541857</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,7 +1236,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 hane med sång i äldre granskog.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1275,7 +1250,32 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1802,7 +1802,7 @@
         <v>132321126</v>
       </c>
       <c r="B11" t="n">
-        <v>96351</v>
+        <v>96352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -1671,61 +1671,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321143</v>
+        <v>132321126</v>
       </c>
       <c r="B10" t="n">
-        <v>58115</v>
+        <v>96352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335257</v>
+        <v>335020</v>
       </c>
       <c r="R10" t="n">
-        <v>6541801</v>
+        <v>6541936</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1762,7 +1750,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>Sparsamt i äldre granskog.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,17 +1759,13 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1799,49 +1783,61 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321126</v>
+        <v>132321143</v>
       </c>
       <c r="B11" t="n">
-        <v>96352</v>
+        <v>58115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335020</v>
+        <v>335257</v>
       </c>
       <c r="R11" t="n">
-        <v>6541936</v>
+        <v>6541801</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,7 +1874,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Sparsamt i äldre granskog.</t>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,13 +1883,17 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -1026,27 +1026,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321212</v>
+        <v>132321158</v>
       </c>
       <c r="B5" t="n">
-        <v>58328</v>
+        <v>57951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,37 +1054,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335044</v>
+        <v>335353</v>
       </c>
       <c r="R5" t="n">
-        <v>6541992</v>
+        <v>6541857</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1109,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>1 hane med sång i äldre granskog.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,7 +1123,32 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1153,27 +1166,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321158</v>
+        <v>132321212</v>
       </c>
       <c r="B6" t="n">
-        <v>57951</v>
+        <v>58328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1181,25 +1194,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335353</v>
+        <v>335044</v>
       </c>
       <c r="R6" t="n">
-        <v>6541857</v>
+        <v>6541992</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1261,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>1 hane med sång i äldre granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,32 +1275,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1671,49 +1671,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321126</v>
+        <v>132321143</v>
       </c>
       <c r="B10" t="n">
-        <v>96352</v>
+        <v>58115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335020</v>
+        <v>335257</v>
       </c>
       <c r="R10" t="n">
-        <v>6541936</v>
+        <v>6541801</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,7 +1762,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt i äldre granskog.</t>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,13 +1771,17 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,61 +1799,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321143</v>
+        <v>132321126</v>
       </c>
       <c r="B11" t="n">
-        <v>58115</v>
+        <v>96352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2810</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335257</v>
+        <v>335020</v>
       </c>
       <c r="R11" t="n">
-        <v>6541801</v>
+        <v>6541936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1874,7 +1878,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>Sparsamt i äldre granskog.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,17 +1887,13 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -1416,32 +1416,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132321211</v>
+        <v>132321144</v>
       </c>
       <c r="B8" t="n">
-        <v>58328</v>
+        <v>58115</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1450,14 +1450,10 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1471,10 +1467,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335168</v>
+        <v>335186</v>
       </c>
       <c r="R8" t="n">
-        <v>6542019</v>
+        <v>6541956</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1511,7 +1507,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare granskog.</t>
+          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,7 +1521,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,32 +1544,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132321144</v>
+        <v>132321211</v>
       </c>
       <c r="B9" t="n">
-        <v>58115</v>
+        <v>58328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1577,10 +1578,14 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1594,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>335186</v>
+        <v>335168</v>
       </c>
       <c r="R9" t="n">
-        <v>6541956</v>
+        <v>6542019</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,7 +1639,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 talltita med lockläte i något tätare barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
+          <t>1 hane med sång i något tätare granskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,12 +1653,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Bitvis flerskiktad barrblandskog med gran, tall, björk och asp.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132321210</v>
+        <v>132321126</v>
       </c>
       <c r="B2" t="n">
-        <v>58331</v>
+        <v>96423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,54 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>335133</v>
+        <v>335020</v>
       </c>
       <c r="R2" t="n">
-        <v>6542070</v>
+        <v>6541936</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare barrblandskog.</t>
+          <t>Sparsamt i äldre granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,12 +763,13 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132321168</v>
+        <v>132321217</v>
       </c>
       <c r="B3" t="n">
-        <v>97990</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>335050</v>
+        <v>335018</v>
       </c>
       <c r="R3" t="n">
-        <v>6542012</v>
+        <v>6541909</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I gammal granskog.</t>
+          <t>I äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132321171</v>
+        <v>132321158</v>
       </c>
       <c r="B4" t="n">
-        <v>97990</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,27 +910,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>335040</v>
+        <v>335353</v>
       </c>
       <c r="R4" t="n">
-        <v>6541915</v>
+        <v>6541857</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +982,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>I äldre granskog.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,13 +991,37 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1026,27 +1039,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132321158</v>
+        <v>132321210</v>
       </c>
       <c r="B5" t="n">
-        <v>57954</v>
+        <v>58349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,25 +1067,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>335353</v>
+        <v>335133</v>
       </c>
       <c r="R5" t="n">
-        <v>6541857</v>
+        <v>6542070</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1134,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>1 hane med sång i något tätare barrblandskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,31 +1149,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132321212</v>
+        <v>132321211</v>
       </c>
       <c r="B6" t="n">
-        <v>58331</v>
+        <v>58349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>335044</v>
+        <v>335168</v>
       </c>
       <c r="R6" t="n">
-        <v>6541992</v>
+        <v>6542019</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1 hane med sång i äldre granskog.</t>
+          <t>1 hane med sång i något tätare granskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1293,32 +1293,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132321145</v>
+        <v>132321212</v>
       </c>
       <c r="B7" t="n">
-        <v>58118</v>
+        <v>58349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1327,10 +1327,14 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1344,10 +1348,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>335274</v>
+        <v>335044</v>
       </c>
       <c r="R7" t="n">
-        <v>6541986</v>
+        <v>6541992</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1384,7 +1388,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Synobservation av 1 talltita med flera varianter av lockläte/övriga läten. I luckig äldre tallskog som omges av ställvis flerskiktad och bitvis tätare barrblandskog med inslag av murknande björkhögstubbar. Mycket lämpliga skogsmiljöer för talltita.</t>
+          <t>1 hane med sång i äldre granskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1398,7 +1402,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1416,32 +1420,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132321211</v>
+        <v>132321143</v>
       </c>
       <c r="B8" t="n">
-        <v>58331</v>
+        <v>58136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1450,14 +1454,10 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1471,10 +1471,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>335168</v>
+        <v>335257</v>
       </c>
       <c r="R8" t="n">
-        <v>6542019</v>
+        <v>6541801</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 hane med sång i något tätare granskog.</t>
+          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,7 +1525,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1546,7 +1551,7 @@
         <v>132321144</v>
       </c>
       <c r="B9" t="n">
-        <v>58118</v>
+        <v>58136</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1671,49 +1676,61 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132321126</v>
+        <v>132321145</v>
       </c>
       <c r="B10" t="n">
-        <v>96355</v>
+        <v>58136</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2810</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gammelskog söder om Södra Backen, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>335020</v>
+        <v>335274</v>
       </c>
       <c r="R10" t="n">
-        <v>6541936</v>
+        <v>6541986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1750,7 +1767,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Sparsamt i äldre granskog.</t>
+          <t>Synobservation av 1 talltita med flera varianter av lockläte/övriga läten. I luckig äldre tallskog som omges av ställvis flerskiktad och bitvis tätare barrblandskog med inslag av murknande björkhögstubbar. Mycket lämpliga skogsmiljöer för talltita.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1759,13 +1776,12 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1783,32 +1799,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132321143</v>
+        <v>132321132</v>
       </c>
       <c r="B11" t="n">
-        <v>58118</v>
+        <v>58131</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>103023</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1820,7 +1836,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1834,10 +1850,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>335257</v>
+        <v>335283</v>
       </c>
       <c r="R11" t="n">
-        <v>6541801</v>
+        <v>6541996</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1872,11 +1888,6 @@
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1 talltita med lockläte i äldre barrblandskog som högst sannolikt ingår i ett revir för talltita. I området finns en mosaik av äldre granskog, tallskog och barrblandskog som bitvis är flerskiktad och murknande björkhögstubbar för talltitans bohål förekommer här. Området hyser mycket bra livsmiljöer för talltita.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1888,12 +1899,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrblandskog.</t>
+          <t>Gles äldre tallskog omgiven av bitvis flerskiktad äldre barrblandskog.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1908,6 +1919,2578 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132321133</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>335098</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6541886</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132321200</v>
+      </c>
+      <c r="B13" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>335071</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6541912</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132321202</v>
+      </c>
+      <c r="B14" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>335015</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6541909</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>I äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132321203</v>
+      </c>
+      <c r="B15" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>335034</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6541942</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I äldre granskog med stor stamdiameterspridning.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132321204</v>
+      </c>
+      <c r="B16" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>335027</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6542022</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>I äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132321266</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>335382</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6541934</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>I gles tallskog.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132321267</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>335255</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6541968</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>I gles äldre tallskog.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132321268</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106358</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221157</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåbär</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Vaccinium myrtillus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>335075</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6541892</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132321168</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>335050</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6542012</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>I gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132321170</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>335382</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6541761</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Växer här i storväxt gammal granskog.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132321171</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>335040</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6541915</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>I äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132321263</v>
+      </c>
+      <c r="B23" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>335368</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6541759</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i storvuxen gammal granskog intill en bäck.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132321237</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>335089</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6541788</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Växer på marken i en luckig yta i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132321239</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>335450</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6541907</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gles tallskog med inslag av björk och gran.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132321240</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>335225</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6541963</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132321241</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>335265</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6541988</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Gles talldominerad öppen äldre skog med renlavar och ljungväxter.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132321242</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>335261</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6542037</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Luckig barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132321246</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>335419</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6541900</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Gles talldominerad skog.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132321247</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>335348</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6541985</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Gles tallskog med ljung.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132321248</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>335365</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6541906</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Luckig, äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132321249</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>335253</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6541972</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bland andra renlavar i gles tallskog.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132321250</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>335295</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6542078</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Gles talldominerad skog.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132321251</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gammelskog söder om Södra Backen, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>335232</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6541994</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ärtemark</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Bitvis flerskiktad luckig barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9460-2026 artfynd.xlsx
+++ b/artfynd/A 9460-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321126</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321217</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321158</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1163,6 +1183,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321210</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1290,6 +1315,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321211</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1417,6 +1447,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321212</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1545,6 +1580,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321143</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1673,6 +1713,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321144</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1796,6 +1841,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321145</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1919,6 +1969,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321132</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2037,6 +2092,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321133</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2144,6 +2204,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321200</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2260,6 +2325,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321202</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2376,6 +2446,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321203</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2492,6 +2567,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321204</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2604,6 +2684,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321266</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2716,6 +2801,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321267</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2823,6 +2913,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321268</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2935,6 +3030,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321168</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3047,6 +3147,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321170</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3159,6 +3264,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321171</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3275,6 +3385,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321263</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3386,6 +3501,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321237</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3497,6 +3617,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321239</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3603,6 +3728,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321240</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3714,6 +3844,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321241</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3825,6 +3960,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321242</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3936,6 +4076,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321246</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4047,6 +4192,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321247</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4158,6 +4308,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321248</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4269,6 +4424,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321249</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4380,6 +4540,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321250</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4491,8 +4656,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132321251</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>